--- a/교육자료/양식/이미지선정표.xlsx
+++ b/교육자료/양식/이미지선정표.xlsx
@@ -703,14 +703,14 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>○  ① 회사 사진 폴더 (구글 드라이브)  https://drive.google.com/drive/folders/14h4Swi9HhV2c5ugAVPLJJg-TKhrMpw4M  ← 가장 먼저 여기서</t>
+          <t>○  ① 회사 사진 폴더 (구글 드라이브)  ← 가장 먼저 여기서. 주소는 계정시트 「참고링크」 시트</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>○  ② 클립아트코리아  clipartkorea.co.kr · 아이디 haodesign01  (비밀번호는 구글 계정 관리 시트)</t>
+          <t>○  ② 클립아트코리아  clipartkorea.co.kr  (계정은 담당자에게 받으세요)</t>
         </is>
       </c>
     </row>
